--- a/internal_doc/05.测试设计/story/alter/altercl测试用例（升级压缩兼容性验证）.xlsx
+++ b/internal_doc/05.测试设计/story/alter/altercl测试用例（升级压缩兼容性验证）.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>name</t>
   </si>
@@ -106,6 +106,29 @@
   <si>
     <t>a场景：升级后修改压缩类型成功，查看cl属性中对应压缩类型为snappy；插入数据后，查看压缩数据压缩类型为snappy（查看对应数据节点snapshot（4）中的DictionaryCreated参数为false）
 b场景：升级后修改操作失败，返回对应错误信息；查看cl属性中对应压缩类型为lzw；插入数据后，查看压缩数据压缩类型为lzw（查看对应数据节点snapshot（4）中的DictionaryCreated参数为true）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旧版本上切分表使用lzw压缩，升级后修改为压缩类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sequoiadb集群运行正常
+2、集群中存在cs、cl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、旧版本上cl设置压缩类型为lzw，插入数据刚好达到构建数据字典条件
+2、执行切分（切分后目标组上没有字典）
+3、升级sdb版本为最新版本
+4、升级后修改压缩类型为snappy，检查操作结果
+5、truncate删除cl数据
+6、修改压缩类型为snappy，检查操作结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、步骤4中修改失败，返回对应错误信息，查看cl属性中压缩类型未更新
+2、步骤6中修改成功，查看cl属性中压缩类型为snappy类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -320,8 +343,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I4" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I5" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I5"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -640,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
@@ -760,6 +783,32 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5" spans="1:9" ht="94.5">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
